--- a/wisestar-client/public/templates/chapter-import-template.xlsx
+++ b/wisestar-client/public/templates/chapter-import-template.xlsx
@@ -413,21 +413,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>学科名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>章节名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>图标(选填)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>排序(选填，数字越小越靠前)</t>
         </is>
@@ -436,31 +441,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>语文</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>识字与写字</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>🖋️</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>古诗文诵读</t>
+          <t>数学</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📜</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
+          <t>100以内加减法</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🧮</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
